--- a/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_pracownik_agenta.xlsx
+++ b/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_pracownik_agenta.xlsx
@@ -120,22 +120,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1283348939</t>
+          <t>1234805466</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0000058216</t>
+          <t>0000000008</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -145,22 +145,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>67061828848</t>
+          <t>60021406849</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2022-11-27</t>
+          <t>27/11/2022</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t/>
+          <t>2015/17/05</t>
         </is>
       </c>
     </row>
@@ -187,22 +187,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1283428124</t>
+          <t>1234884655</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0000058313</t>
+          <t>0000000105</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -217,17 +217,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>68071930237</t>
+          <t>61032108236</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-04-28</t>
+          <t>2021/28/04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t/>
+          <t>24-06-2016</t>
         </is>
       </c>
     </row>
@@ -254,22 +254,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1283586509</t>
+          <t>1234963840</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0000058410</t>
+          <t>0000000202</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -284,17 +284,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>69082031584</t>
+          <t>62042809586</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2022-04-18</t>
+          <t>18-04-2022</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-09-30</t>
+          <t>2024-30-09</t>
         </is>
       </c>
     </row>
@@ -321,22 +321,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1283586509</t>
+          <t>1235043030</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0000058507</t>
+          <t>0000000299</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -351,17 +351,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>70092132978</t>
+          <t>63050710972</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2018-12-26</t>
+          <t>2018-26-12</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t/>
+          <t>20180810</t>
         </is>
       </c>
     </row>
@@ -388,7 +388,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -398,12 +398,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1283665692</t>
+          <t>1235122226</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0000058604</t>
+          <t>0000000396</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -418,17 +418,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>71102234329</t>
+          <t>64061412321</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2018-08-13</t>
+          <t>20180813</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2019</t>
         </is>
       </c>
     </row>
@@ -455,22 +455,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cieślicka</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1283744888</t>
+          <t>1235201411</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0000058701</t>
+          <t>0000000493</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -485,17 +485,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>72112335714</t>
+          <t>65072113717</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2021-05-24</t>
+          <t>24/05/2021</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t/>
+          <t>2020/24/10</t>
         </is>
       </c>
     </row>
@@ -522,22 +522,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1283824073</t>
+          <t>1235280600</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0000058798</t>
+          <t>0000000590</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -552,17 +552,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>73122437063</t>
+          <t>66082815068</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2021-08-01</t>
+          <t>2021/01/08</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>01-06-2025</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PZU SA</t>
+          <t>PZU AS</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -589,22 +589,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1283903269</t>
+          <t>1235359796</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0000058895</t>
+          <t>0000000687</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -614,22 +614,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Zielińsik</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>74012538453</t>
+          <t>67090716451</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2022-09-19</t>
+          <t>19-09-2022</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t/>
+          <t>2022-10-12</t>
         </is>
       </c>
     </row>
@@ -656,22 +656,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kwiatkowska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1283982458</t>
+          <t>1235438981</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0000058992</t>
+          <t>0000000784</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>75022639800</t>
+          <t>68101417802</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2018-12-01</t>
+          <t>2018-01-12</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t/>
+          <t>20230117</t>
         </is>
       </c>
     </row>
@@ -723,22 +723,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1284061648</t>
+          <t>1235518177</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0000059089</t>
+          <t>0000000881</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -753,17 +753,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>76032741190</t>
+          <t>79112119190</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2018-08-28</t>
+          <t>20180828</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t/>
+          <t>24/02/2024</t>
         </is>
       </c>
     </row>
@@ -790,22 +790,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1284140833</t>
+          <t>2235597366</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0000059186</t>
+          <t>0000000978</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -820,17 +820,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>77042842547</t>
+          <t>70122820541</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>26/04/2018</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026/06/02</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1284220029</t>
+          <t>1235676551</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0000059283</t>
+          <t>0000001075</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -887,17 +887,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>78050143938</t>
+          <t>71010721939</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2023-11-25</t>
+          <t>2023/25/11</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>27-04-2026</t>
         </is>
       </c>
     </row>
@@ -924,22 +924,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1284378405</t>
+          <t>1235755747</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0000059380</t>
+          <t>0000001172</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -954,17 +954,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>79060245287</t>
+          <t>72021423289</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2018-01-29</t>
+          <t>29-01-2018</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t/>
+          <t>2015-17-05</t>
         </is>
       </c>
     </row>
@@ -991,22 +991,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Malgorzata</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cieslicka</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1284378405</t>
+          <t>1235834932</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0000059477</t>
+          <t>0000001269</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>80070346671</t>
+          <t>73032124675</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2021-02-26</t>
+          <t>2021-26-02</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t/>
+          <t>20160624</t>
         </is>
       </c>
     </row>
@@ -1058,22 +1058,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1284457599</t>
+          <t>1235914128</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0000059574</t>
+          <t>0000001366</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1088,17 +1088,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>81080448029</t>
+          <t>74042826025</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2018-10-16</t>
+          <t>20181016</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t/>
+          <t>03/07/2017</t>
         </is>
       </c>
     </row>
@@ -1125,22 +1125,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1284536784</t>
+          <t>1235993317</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0000059671</t>
+          <t>0000001463</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>82090549414</t>
+          <t>75050727418</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2019-02-19</t>
+          <t>19/02/2019</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026/24/02</t>
         </is>
       </c>
     </row>
@@ -1192,22 +1192,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1284695169</t>
+          <t>1236072507</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0000059768</t>
+          <t>0000001560</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>83100650768</t>
+          <t>76061428767</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2019-01-15</t>
+          <t>2019/15/01</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t/>
+          <t>17-09-2019</t>
         </is>
       </c>
     </row>
@@ -1259,22 +1259,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t/>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1284695169</t>
+          <t>1236151690</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0000059865</t>
+          <t>0000001657</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1289,17 +1289,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>84110752154</t>
+          <t>77072130157</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2020-03-19</t>
+          <t>18-04-2020</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t/>
+          <t>2020-24-10</t>
         </is>
       </c>
     </row>
@@ -1326,22 +1326,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1284774354</t>
+          <t>1236230886</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0000059962</t>
+          <t>0000001754</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1356,17 +1356,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>85120853501</t>
+          <t>78082831506</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2019-11-20</t>
+          <t>2019-20-11</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2024-11-02</t>
+          <t>20241102</t>
         </is>
       </c>
     </row>
@@ -1393,22 +1393,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cieślicki</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1284932735</t>
+          <t>1236310071</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0000060059</t>
+          <t>0000001851</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>86010954892</t>
+          <t>79090732890</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>20251112</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>22/05/2025</t>
         </is>
       </c>
     </row>
@@ -1460,22 +1460,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kozłowska</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1284932735</t>
+          <t>1236389262</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0000060156</t>
+          <t>0000001948</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1490,17 +1490,17 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>87021056249</t>
+          <t>80101434241</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>30/03/2025</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025/26/04</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1527,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1285011925</t>
+          <t>1236468458</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0000060253</t>
+          <t>0000002045</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1557,17 +1557,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>88031157634</t>
+          <t>81112135637</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2024-10-18</t>
+          <t>2024/18/10</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>10-05-2026</t>
         </is>
       </c>
     </row>
@@ -1594,29 +1594,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tomaszewska</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1236547643</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0000002142</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Duda</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1285091114</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0000060350</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>Stępień</t>
@@ -1624,17 +1624,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>89041258982</t>
+          <t>82122836987</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2020-02-26</t>
+          <t>26-02-2020</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-03-03</t>
         </is>
       </c>
     </row>
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1285249495</t>
+          <t>1236626839</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0000060447</t>
+          <t>0000002239</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1691,17 +1691,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>90051360370</t>
+          <t>83010738376</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>20251106</t>
         </is>
       </c>
     </row>
@@ -1728,29 +1728,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pietrzak</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1236706024</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0000002336</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>Ewa</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Zielińska</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1285249495</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>0000060544</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Rutkowska</t>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>91061461727</t>
+          <t>84021439724</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2023-12-21</t>
+          <t>20231221</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>05/05/2025</t>
         </is>
       </c>
     </row>
@@ -1795,22 +1795,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1285328680</t>
+          <t>1236785213</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0000060641</t>
+          <t>0000002433</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1825,17 +1825,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>92071563113</t>
+          <t>85032141114</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
+          <t>25/05/2023</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t/>
+          <t>2016/24/06</t>
         </is>
       </c>
     </row>
@@ -1862,22 +1862,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Piotrowska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1285407876</t>
+          <t>1236864409</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0000060738</t>
+          <t>0000002530</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1892,17 +1892,17 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>93081664461</t>
+          <t>86042842464</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2019/25/02</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t/>
+          <t>03-07-2017</t>
         </is>
       </c>
     </row>
@@ -1929,22 +1929,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1285487065</t>
+          <t>1236943592</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0000060835</t>
+          <t>0000002627</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1959,17 +1959,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>94091765856</t>
+          <t>87050743857</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
+          <t>16-09-2019</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t/>
+          <t>2018-10-08</t>
         </is>
       </c>
     </row>
@@ -1996,22 +1996,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1285566250</t>
+          <t>1237022782</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0000060932</t>
+          <t>0000002724</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>95101867207</t>
+          <t>88061445206</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>20260611</t>
         </is>
       </c>
     </row>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1285645446</t>
+          <t>1237101978</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0000061029</t>
+          <t>0000002821</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>96111968593</t>
+          <t>89072146593</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2021-03-16</t>
+          <t>20210316</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>05/08/2026</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1285724631</t>
+          <t>1237181167</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0000061126</t>
+          <t>0000002918</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2160,17 +2160,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>97122069949</t>
+          <t>90082847941</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2020-01-14</t>
+          <t>14/01/2020</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t/>
+          <t>2021/03/11</t>
         </is>
       </c>
     </row>
@@ -2197,22 +2197,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Wojciechowska</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1285803827</t>
+          <t>1237260352</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0000061223</t>
+          <t>0000003015</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>98012171333</t>
+          <t>91090749335</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2022/26/09</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>26-08-2024</t>
         </is>
       </c>
     </row>
@@ -2264,22 +2264,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1285883016</t>
+          <t>1237418735</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0000061320</t>
+          <t>0000003112</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2294,17 +2294,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>99022272681</t>
+          <t>92101450680</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2018-02-19</t>
+          <t>19-02-2018</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-17-01</t>
         </is>
       </c>
     </row>
@@ -2331,22 +2331,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kaimńska</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1285962201</t>
+          <t>1237418735</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0000061417</t>
+          <t>0000003209</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2361,17 +2361,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>00232374072</t>
+          <t>93112152077</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-29-08</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t/>
+          <t>20240224</t>
         </is>
       </c>
     </row>
@@ -2398,22 +2398,22 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Kowalska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1286120585</t>
+          <t>1237497924</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0000061514</t>
+          <t>0000003306</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2428,17 +2428,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>01242475429</t>
+          <t>94122853426</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2022-08-24</t>
+          <t>20220824</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t/>
+          <t>03/03/2025</t>
         </is>
       </c>
     </row>
@@ -2465,22 +2465,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jasieński</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1286120585</t>
+          <t>1237656305</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0000061611</t>
+          <t>0000003403</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>02252576814</t>
+          <t>95010754814</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2021-06-03</t>
+          <t>03/06/2021</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t/>
+          <t>2026/10/04</t>
         </is>
       </c>
     </row>
@@ -2532,22 +2532,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1286199776</t>
+          <t>1237656305</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0000061708</t>
+          <t>0000003500</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2562,17 +2562,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>03262678163</t>
+          <t>96021456164</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2023/01/05</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2024-11-01</t>
+          <t>01-11-2024</t>
         </is>
       </c>
     </row>
@@ -2599,22 +2599,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jasieński</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1286278961</t>
+          <t>1237735499</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0000061805</t>
+          <t>0000003597</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>04272779558</t>
+          <t>97032157550</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2020-09-18</t>
+          <t>18-09-2020</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2024-08-19</t>
+          <t>2024-19-08</t>
         </is>
       </c>
     </row>
@@ -2666,22 +2666,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cieślicki</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1286358157</t>
+          <t>1237814684</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0000061902</t>
+          <t>0000003694</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2696,17 +2696,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>05282880908</t>
+          <t>98042858909</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2018-08-07</t>
+          <t>2018-07-08</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>20250822</t>
         </is>
       </c>
     </row>
@@ -2733,22 +2733,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cieślar</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1286437342</t>
+          <t>1237893873</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0000061999</t>
+          <t>0000003791</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2763,17 +2763,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>60090182297</t>
+          <t>99050760297</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>20251016</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t/>
+          <t>10/08/2018</t>
         </is>
       </c>
     </row>
@@ -2800,22 +2800,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1286516538</t>
+          <t>1237973069</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0000062096</t>
+          <t>0000003888</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2825,22 +2825,22 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>61100283647</t>
+          <t>00261461640</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2021-06-19</t>
+          <t>19/06/2021</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025/27/02</t>
         </is>
       </c>
     </row>
@@ -2867,22 +2867,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1286595727</t>
+          <t>1238052259</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0000062193</t>
+          <t>0000003985</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2897,17 +2897,17 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>62110385033</t>
+          <t>01272163037</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2021-12-30</t>
+          <t>2021/30/12</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t/>
+          <t>24-10-2020</t>
         </is>
       </c>
     </row>
@@ -2934,22 +2934,22 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kwiatkowska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1286674912</t>
+          <t>1238131444</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0000062290</t>
+          <t>0000004082</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2964,17 +2964,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>63120486381</t>
+          <t>02282864387</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>22-06-2025</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t/>
+          <t>2021-03-11</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3001,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1286754108</t>
+          <t>1238289820</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0000062387</t>
+          <t>0000004179</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>64010587771</t>
+          <t>03290765770</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2024-05-20</t>
+          <t>2024-20-05</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2024-06-06</t>
+          <t>20240606</t>
         </is>
       </c>
     </row>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1286833291</t>
+          <t>1238289820</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0000062484</t>
+          <t>0000004276</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3098,17 +3098,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>65020689129</t>
+          <t>04301467122</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2018-11-23</t>
+          <t>20181123</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>05/01/2025</t>
         </is>
       </c>
     </row>
@@ -3135,22 +3135,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Paweł</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1286912487</t>
+          <t>1238369016</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0000062581</t>
+          <t>0000004373</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>66030790517</t>
+          <t>05312168518</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2020-03-31</t>
+          <t>31/03/2020</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024/08/08</t>
         </is>
       </c>
     </row>
@@ -3202,29 +3202,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Woźniak</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1238448201</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0000004470</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>Monika</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Kozłowska</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1286991676</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>0000062678</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
           <t>Lewandowska</t>
@@ -3232,17 +3232,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>67040891865</t>
+          <t>60122869864</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2022-06-11</t>
+          <t>2022/11/06</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>06-05-2025</t>
         </is>
       </c>
     </row>
@@ -3269,22 +3269,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1287070866</t>
+          <t>1238527395</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0000062775</t>
+          <t>000000456</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3299,17 +3299,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>68050993251</t>
+          <t>61010771256</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2019-10-17</t>
+          <t>17-10-2019</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-08-05</t>
         </is>
       </c>
     </row>
@@ -3336,22 +3336,22 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1287150051</t>
+          <t>1238606580</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0000062872</t>
+          <t>0000004664</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3366,17 +3366,17 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>69061094607</t>
+          <t>62021472604</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-21-09</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t/>
+          <t>20150517</t>
         </is>
       </c>
     </row>
@@ -3403,22 +3403,22 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kwiatkowska</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1287229249</t>
+          <t>1238764965</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0000062969</t>
+          <t>0000004761</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>70071195992</t>
+          <t>63032173991</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2019-03-24</t>
+          <t>20190324</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t/>
+          <t>24/06/2016</t>
         </is>
       </c>
     </row>
@@ -3470,22 +3470,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kwiatkowski</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1287308434</t>
+          <t>1238764965</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0000063066</t>
+          <t>0000004858</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3500,17 +3500,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>71081297340</t>
+          <t>64042875341</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2023-07-06</t>
+          <t>06/07/2023</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t/>
+          <t>2017/03/07</t>
         </is>
       </c>
     </row>
@@ -3537,22 +3537,22 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kozłowska</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1287387623</t>
+          <t>1238844150</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0000063163</t>
+          <t>0000004955</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>72091398735</t>
+          <t>65050776734</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2023-02-18</t>
+          <t>2023/18/02</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t/>
+          <t>10-08-2018</t>
         </is>
       </c>
     </row>
@@ -3604,22 +3604,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1287466819</t>
+          <t>1238923346</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>0000063260</t>
+          <t>0000005052</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3634,17 +3634,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>73101400080</t>
+          <t>66061478084</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2018-07-26</t>
+          <t>26-07-2018</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t/>
+          <t>2019-17-09</t>
         </is>
       </c>
     </row>
@@ -3671,22 +3671,22 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kowalski</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1287546004</t>
+          <t>1239002536</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0000063357</t>
+          <t>0000005149</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>74111501475</t>
+          <t>67072179470</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2018-08-12</t>
+          <t>2018-12-08</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t/>
+          <t>20201024</t>
         </is>
       </c>
     </row>
@@ -3738,22 +3738,22 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1287625198</t>
+          <t>1239081725</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0000063454</t>
+          <t>0000005246</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3768,17 +3768,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>75121602822</t>
+          <t>68082880822</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2020-07-31</t>
+          <t>20200731</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>20/12/2024</t>
         </is>
       </c>
     </row>
@@ -3805,22 +3805,22 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Wojciechowski</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1287704383</t>
+          <t>1239160910</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0000063551</t>
+          <t>0000005343</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>76011704213</t>
+          <t>69090782216</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2019-08-31</t>
+          <t>31/08/2019</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026/28/10</t>
         </is>
       </c>
     </row>
@@ -3877,17 +3877,17 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1287783572</t>
+          <t>1239240106</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>0000063648</t>
+          <t>0000005440</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3902,17 +3902,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>77021805561</t>
+          <t>70101483567</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2022-01-15</t>
+          <t>2022/15/01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t/>
+          <t>17-01-2023</t>
         </is>
       </c>
     </row>
@@ -3939,27 +3939,27 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1287862768</t>
+          <t>1239319291</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0000063745</t>
+          <t>0000005537</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mare</t>
+          <t>Marke</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3969,17 +3969,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>78031906956</t>
+          <t>71112184953</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2025-05-04</t>
+          <t>04-05-2025</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t/>
+          <t>2024-24-02</t>
         </is>
       </c>
     </row>
@@ -4006,22 +4006,22 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1287941953</t>
+          <t>1239398480</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0000063842</t>
+          <t>0000005634</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>79042008303</t>
+          <t>72122886303</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2019-11-12</t>
+          <t>2019-12-11</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t/>
+          <t>20250303</t>
         </is>
       </c>
     </row>
@@ -4073,22 +4073,22 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wojciechowski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1288021143</t>
+          <t>2239477676</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0000063939</t>
+          <t>0000005731</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4103,17 +4103,17 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>90052109698</t>
+          <t>83010787692</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>20250917</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -4140,22 +4140,22 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1288100339</t>
+          <t>1239556861</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0000064036</t>
+          <t>0000005828</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4170,17 +4170,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>81062211049</t>
+          <t>74021489041</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>2018-07-17</t>
+          <t>17/07/2018</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025/06/10</t>
         </is>
       </c>
     </row>
@@ -4207,22 +4207,22 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1288258715</t>
+          <t>1239636057</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0000064133</t>
+          <t>0000005925</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4237,17 +4237,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>82072312434</t>
+          <t>75032190430</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2019-07-30</t>
+          <t>2019/30/07</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t/>
+          <t>24-06-2016</t>
         </is>
       </c>
     </row>
@@ -4274,22 +4274,22 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jasieński</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1288258715</t>
+          <t>1239715242</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0000064230</t>
+          <t>0000006022</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4304,17 +4304,17 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>83082413782</t>
+          <t>76042891780</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>2024-08-27</t>
+          <t>27-08-2024</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t/>
+          <t>2017-03-07</t>
         </is>
       </c>
     </row>
@@ -4341,22 +4341,22 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1288337900</t>
+          <t>1239794431</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0000064327</t>
+          <t>0000006119</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4371,17 +4371,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>84092515178</t>
+          <t>77050793174</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2020-11-04</t>
+          <t>2020-04-11</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t/>
+          <t>2018-10-08 07:37</t>
         </is>
       </c>
     </row>
@@ -4408,22 +4408,22 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1288417094</t>
+          <t>1239873627</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0000064424</t>
+          <t>0000006216</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4438,17 +4438,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>85102616528</t>
+          <t>78061494522</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2019-10-06</t>
+          <t>20191006</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>2024-02-23</t>
+          <t>23/02/2024</t>
         </is>
       </c>
     </row>
@@ -4475,22 +4475,22 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kwiatkowska</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1288496283</t>
+          <t>1239952812</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0000064521</t>
+          <t>0000006313</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4505,17 +4505,17 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>86112717913</t>
+          <t>79072195918</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>26/04/2018</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025/01/04</t>
         </is>
       </c>
     </row>
@@ -4542,22 +4542,22 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Magdalona</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2288575479</t>
+          <t>1240032000</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0000064618</t>
+          <t>0000006410</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>87122819262</t>
+          <t>80082897268</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2021-04-14</t>
+          <t>2021/14/04</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t/>
+          <t>03-11-2021</t>
         </is>
       </c>
     </row>
@@ -4609,22 +4609,22 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Piotrowska</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1288654664</t>
+          <t>1240111194</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0000064715</t>
+          <t>0000006507</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4639,17 +4639,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>88010120651</t>
+          <t>81090798651</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>09-01-2025</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>2024-12-05</t>
+          <t>2024-05-12</t>
         </is>
       </c>
     </row>
@@ -4676,22 +4676,22 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1288813045</t>
+          <t>1240190383</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0000064812</t>
+          <t>0000006604</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>89020222009</t>
+          <t>82101400006</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-28-02</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t/>
+          <t>20230117</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1288813045</t>
+          <t>1240269570</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0000064909</t>
+          <t>0000006701</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4773,17 +4773,17 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>90030323394</t>
+          <t>83112101393</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2021-05-16</t>
+          <t>202105160713</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t/>
+          <t>24/02/2024</t>
         </is>
       </c>
     </row>
@@ -4810,22 +4810,22 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Jaseńska</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1288892234</t>
+          <t>1240348766</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0000065006</t>
+          <t>0000006798</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4840,17 +4840,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>91040424741</t>
+          <t>84122802742</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2020-10-13</t>
+          <t>13/10/2020</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025/02/10</t>
         </is>
       </c>
     </row>
@@ -4877,22 +4877,22 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1289129807</t>
+          <t>1240427951</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0000065103</t>
+          <t>0000006895</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4907,17 +4907,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>92050526137</t>
+          <t>85010704131</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2024-06-22</t>
+          <t>2024/22/06</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t/>
+          <t>10-04-2026</t>
         </is>
       </c>
     </row>
@@ -4944,22 +4944,22 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1289129807</t>
+          <t>1240507147</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0000065200</t>
+          <t>0000006992</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4974,17 +4974,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>93060627485</t>
+          <t>86021405480</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>19-03-2023</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t/>
+          <t>2015-17-05</t>
         </is>
       </c>
     </row>
@@ -5016,17 +5016,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1289129807</t>
+          <t>1240586336</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0000065297</t>
+          <t>0000007089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>94070728870</t>
+          <t>87032106876</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>20260608</t>
         </is>
       </c>
     </row>
@@ -5078,22 +5078,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Kowalska</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1289208990</t>
+          <t>1240665521</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0000065394</t>
+          <t>0000007186</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5108,17 +5108,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>95080830221</t>
+          <t>88042808226</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>2020-01-31</t>
+          <t>20200131</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>19/05/2025</t>
         </is>
       </c>
     </row>
@@ -5145,22 +5145,22 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1289367375</t>
+          <t>1240744717</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0000065491</t>
+          <t>0000007283</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5175,17 +5175,17 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>96090931616</t>
+          <t>89050709619</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>13/02/2025</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t/>
+          <t>2018/10/08</t>
         </is>
       </c>
     </row>
@@ -5212,22 +5212,22 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1289367375</t>
+          <t>1240823902</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0000065588</t>
+          <t>0000007380</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5242,17 +5242,17 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>97101032966</t>
+          <t>90061410960</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2023-11-03</t>
+          <t>2023/03/11</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t/>
+          <t>17-09-2019</t>
         </is>
       </c>
     </row>
@@ -5279,22 +5279,22 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Patrycja</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1289446560</t>
+          <t>1240903096</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0000065685</t>
+          <t>0000007477</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5309,17 +5309,17 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>98111134352</t>
+          <t>91072112357</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>2019-04-27</t>
+          <t>27-04-2019</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-10</t>
         </is>
       </c>
     </row>
@@ -5346,22 +5346,22 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1289525756</t>
+          <t>1240982285</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0000065782</t>
+          <t>0000007574</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5376,17 +5376,17 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>99121235709</t>
+          <t>92082813706</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2020-03-24</t>
+          <t>2020-24-03</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>2024-04-02</t>
+          <t>20240402</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1289604941</t>
+          <t>1241061475</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0000065879</t>
+          <t>0000007671</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5443,17 +5443,17 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>00211337096</t>
+          <t>93090715091</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2021-05-04</t>
+          <t>20210504</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>21/05/2025</t>
         </is>
       </c>
     </row>
@@ -5480,22 +5480,22 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1289684130</t>
+          <t>1241140660</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>0000065976</t>
+          <t>0000007768</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5505,22 +5505,22 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>01221438443</t>
+          <t>94101416442</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>16/05/2022</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025/30/09</t>
         </is>
       </c>
     </row>
@@ -5547,22 +5547,22 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Piotrowski</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1289763326</t>
+          <t>1241219858</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0000066073</t>
+          <t>0000007865</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>02231539838</t>
+          <t>95112117838</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2022-03-05</t>
+          <t>2022/05/03</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t/>
+          <t>24-02-2024</t>
         </is>
       </c>
     </row>
@@ -5614,27 +5614,27 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pawłowska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1289842511</t>
+          <t/>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0000066170</t>
+          <t>0000007962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t/>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>03241641180</t>
+          <t>96122819189</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>22-02-2025</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-03-03</t>
         </is>
       </c>
     </row>
@@ -5681,29 +5681,29 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>Rafał</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Dąbrowski</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1241378232</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0000008059</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
           <t>Krzysztof</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Jasieński</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>1289921707</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>0000066267</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Krzysztof</t>
-        </is>
-      </c>
       <c r="J85" t="inlineStr">
         <is>
           <t>Wójcik</t>
@@ -5711,17 +5711,17 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>04251742575</t>
+          <t>97010720570</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-31-10</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>20240715</t>
         </is>
       </c>
     </row>
@@ -5748,22 +5748,22 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1290000893</t>
+          <t>1241457428</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0000066364</t>
+          <t>0000008156</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5778,17 +5778,17 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>05261843922</t>
+          <t>98021421928</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2020-03-14</t>
+          <t>20200314</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t/>
+          <t>17/05/2015</t>
         </is>
       </c>
     </row>
@@ -5815,22 +5815,22 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kozłowska</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1290080082</t>
+          <t>1241536613</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0000066461</t>
+          <t>0000008253</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5845,17 +5845,17 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>60071945314</t>
+          <t>99032123315</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2019-08-18</t>
+          <t>18/08/2019</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024/14/08</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cieślicka</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0000066558</t>
+          <t>0000008350</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5912,17 +5912,17 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>61082046661</t>
+          <t>00242824660</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025/02/07</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>16-04-2025</t>
         </is>
       </c>
     </row>
@@ -5954,17 +5954,17 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1290238465</t>
+          <t>1241694996</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0000066655</t>
+          <t>0000008447</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5979,17 +5979,17 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>62092148057</t>
+          <t>01250726054</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>14-09-2025</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -6016,22 +6016,22 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1290317650</t>
+          <t>1241774181</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0000066752</t>
+          <t>0000008544</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6046,17 +6046,17 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>63102249407</t>
+          <t>02261427402</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2021-02-25</t>
+          <t>2021-25-02</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>20251008</t>
         </is>
       </c>
     </row>
@@ -6083,22 +6083,22 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1290476035</t>
+          <t>1241853377</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0000066849</t>
+          <t>0000008641</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6113,17 +6113,17 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>64112350796</t>
+          <t>03272128799</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2018-06-08</t>
+          <t>20180608</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2024-03-09</t>
+          <t>09/03/2024</t>
         </is>
       </c>
     </row>
@@ -6150,22 +6150,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Piotrowski</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1290476035</t>
+          <t>1241932562</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0000066946</t>
+          <t>0000008738</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6180,17 +6180,17 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>65122452144</t>
+          <t>04282830142</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>24/09/2025</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026/12/05</t>
         </is>
       </c>
     </row>
@@ -6217,22 +6217,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1290555220</t>
+          <t>1242011752</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0000067043</t>
+          <t>0000008835</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6247,17 +6247,17 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>66012553534</t>
+          <t>05290731535</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2019-02-19</t>
+          <t>2019/19/02</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>07-08-2025</t>
         </is>
       </c>
     </row>
@@ -6284,29 +6284,29 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Wieczorek</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1242090941</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>0000008932</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Piotrowska</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>1290634416</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>0000067140</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>Woźniak</t>
@@ -6314,17 +6314,17 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>67022654882</t>
+          <t>60101432883</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2018-05-25</t>
+          <t>25-05-2018</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t/>
+          <t>2023-17-01</t>
         </is>
       </c>
     </row>
@@ -6351,22 +6351,22 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1290713601</t>
+          <t>1242170137</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>0000067237</t>
+          <t>0000009029</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6381,17 +6381,17 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>68032756278</t>
+          <t>61112134270</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2018-07-02</t>
+          <t>2018-02-07</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t/>
+          <t>20240224</t>
         </is>
       </c>
     </row>
@@ -6418,22 +6418,22 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1290792799</t>
+          <t>1242249324</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>0000067334</t>
+          <t>0000009126</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6448,17 +6448,17 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>69042857625</t>
+          <t>62122835629</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>20200308</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>25/07/2025</t>
         </is>
       </c>
     </row>
@@ -6485,22 +6485,22 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1290871984</t>
+          <t>1242407705</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>0000067431</t>
+          <t>0000009223</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6515,17 +6515,17 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>70050159016</t>
+          <t>63010737018</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2019-10-26</t>
+          <t>26/10/2019</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t/>
+          <t>2026/10/04</t>
         </is>
       </c>
     </row>
@@ -6552,22 +6552,22 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1291109557</t>
+          <t>1242407705</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>0000067528</t>
+          <t>0000009320</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6582,17 +6582,17 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>71060260367</t>
+          <t>64021438367</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2024-11-15</t>
+          <t>2024/15/11</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>10-06-2026</t>
         </is>
       </c>
     </row>
@@ -6619,22 +6619,22 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1291109557</t>
+          <t>1242486892</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0000067625</t>
+          <t>000000941</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6649,17 +6649,17 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>72070361752</t>
+          <t>65032139753</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2019-11-20</t>
+          <t>20-11-2019</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-24-06</t>
         </is>
       </c>
     </row>
@@ -6686,22 +6686,22 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1291109557</t>
+          <t>1242566088</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>0000067722</t>
+          <t>0000009514</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6716,17 +6716,17 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>73080463100</t>
+          <t>66042841106</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2020-06-28</t>
+          <t>2020-28-06</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t/>
+          <t>20170703</t>
         </is>
       </c>
     </row>
@@ -6753,22 +6753,22 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lewandowski</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1291188746</t>
+          <t>1242645273</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>0000067819</t>
+          <t>0000009611</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6783,17 +6783,17 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>74090564496</t>
+          <t>67050742490</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2024-08-03</t>
+          <t>20240803</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t/>
+          <t>10/08/2018</t>
         </is>
       </c>
     </row>
@@ -6820,22 +6820,22 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1291267931</t>
+          <t>1242724469</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>0000067916</t>
+          <t>0000009708</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6850,17 +6850,17 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>75100665846</t>
+          <t>68061443848</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2018-07-01</t>
+          <t>01/07/2018</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026/13/07</t>
         </is>
       </c>
     </row>
@@ -6887,22 +6887,22 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1291347127</t>
+          <t>1242803654</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>0000068013</t>
+          <t>0000009805</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6917,17 +6917,17 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>76110767232</t>
+          <t>69072145235</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025/11/02</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t/>
+          <t>24-10-2020</t>
         </is>
       </c>
     </row>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Pawłowska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1291426312</t>
+          <t>1242882843</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>0000068110</t>
+          <t>0000009902</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6984,17 +6984,17 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>77120868580</t>
+          <t>70082846584</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>19-11-2024</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-08-06</t>
         </is>
       </c>
     </row>
@@ -7021,22 +7021,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1291505508</t>
+          <t>1242962039</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>0000068207</t>
+          <t>0000009999</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7051,17 +7051,17 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>78010969970</t>
+          <t>71090747977</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2019-05-03</t>
+          <t>2019-03-05</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>20240723</t>
         </is>
       </c>
     </row>
@@ -7088,22 +7088,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Wojciechowski</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1291584695</t>
+          <t>1243041229</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>0000068304</t>
+          <t>0000010096</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -7118,17 +7118,17 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>79021071320</t>
+          <t>72101449329</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2019-07-17</t>
+          <t>20190717</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t/>
+          <t>17/01/2023</t>
         </is>
       </c>
     </row>
@@ -7155,22 +7155,22 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1291663880</t>
+          <t>1243120414</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>0000068401</t>
+          <t>0000010193</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7185,17 +7185,17 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>80031172714</t>
+          <t>73112150718</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>13/06/2025</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t/>
+          <t>2024/24/02</t>
         </is>
       </c>
     </row>
@@ -7222,22 +7222,22 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1291743076</t>
+          <t>1243199605</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>0000068498</t>
+          <t>0000010290</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7252,17 +7252,17 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>81041274063</t>
+          <t>74122852069</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2023-06-13</t>
+          <t>2023/13/06</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>24-02-2026</t>
         </is>
       </c>
     </row>
@@ -7289,22 +7289,22 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Andrzej</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pawłowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1291822261</t>
+          <t>1243278799</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>0000068595</t>
+          <t>0000010387</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7314,22 +7314,22 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Ostrowsk</t>
+          <t>Ostorwski</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>82051375458</t>
+          <t>75010753457</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2019-02-07</t>
+          <t>07-02-2019</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -7356,22 +7356,22 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Piotrowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1291901457</t>
+          <t>1243357984</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>0000068692</t>
+          <t>0000010484</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7386,17 +7386,17 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>83061476805</t>
+          <t>76021454805</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-29-09</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>20240326</t>
         </is>
       </c>
     </row>
@@ -7423,22 +7423,22 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1291980646</t>
+          <t>2243516365</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>0000068789</t>
+          <t>0000010581</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>84071578192</t>
+          <t>87032156193</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2023-01-22</t>
+          <t>20230122</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t/>
+          <t>24/06/2016</t>
         </is>
       </c>
     </row>
@@ -7490,22 +7490,22 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cieślar</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1292059838</t>
+          <t>1243516365</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>0000068886</t>
+          <t>0000010678</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7520,17 +7520,17 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>85081679549</t>
+          <t>78042857542</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>2025-06-30</t>
+          <t>2025/30/06</t>
         </is>
       </c>
     </row>
@@ -7557,22 +7557,22 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1292139023</t>
+          <t>1243595554</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>0000068983</t>
+          <t>0000010775</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7587,17 +7587,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>86091780937</t>
+          <t>79050758935</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2019/19/08</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>06-07-2026</t>
         </is>
       </c>
     </row>
@@ -7624,22 +7624,22 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1292218219</t>
+          <t>1243753935</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>0000069080</t>
+          <t>0000010872</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7654,17 +7654,17 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>87101882289</t>
+          <t>80061460287</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2019-10-14</t>
+          <t>14-10-2019</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-15-10</t>
         </is>
       </c>
     </row>
@@ -7691,22 +7691,22 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1292297408</t>
+          <t>1243753935</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>0000069177</t>
+          <t>0000010969</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>88111983674</t>
+          <t>81072161673</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t/>
+          <t>20201024</t>
         </is>
       </c>
     </row>
@@ -7758,22 +7758,22 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Kowalska</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1292376591</t>
+          <t>1243833120</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>0000069274</t>
+          <t/>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>89122085021</t>
+          <t>82082863023</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2018-01-17</t>
+          <t>20180117</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2024-02-22</t>
+          <t>22/02/2024</t>
         </is>
       </c>
     </row>
@@ -7825,22 +7825,22 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Dorota</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kozłowska</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1292455787</t>
+          <t>1243912316</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>0000069371</t>
+          <t>0000011163</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7855,17 +7855,17 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>90012186410</t>
+          <t>83090764416</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2020-07-26</t>
+          <t>26/07/2020</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t/>
+          <t>2022/10/12</t>
         </is>
       </c>
     </row>
@@ -7892,22 +7892,22 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1292534972</t>
+          <t>1243991505</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>0000069468</t>
+          <t>0000011260</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7922,17 +7922,17 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>91022287768</t>
+          <t>84101465768</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2019-08-25</t>
+          <t>2019/25/08</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t/>
+          <t>17-01-2023</t>
         </is>
       </c>
     </row>
@@ -7959,22 +7959,22 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1292614168</t>
+          <t>1244070693</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>0000069565</t>
+          <t>0000011357</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7989,17 +7989,17 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>92032389154</t>
+          <t>85112167155</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2021-12-29</t>
+          <t>29-12-2021</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-31-03</t>
         </is>
       </c>
     </row>
@@ -8026,22 +8026,22 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1292693357</t>
+          <t>1244149880</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>0000069662</t>
+          <t>0000011454</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8056,17 +8056,17 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>93042490504</t>
+          <t>86122868504</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2023-27-07</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>20250331</t>
         </is>
       </c>
     </row>
@@ -8093,22 +8093,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Cieślar</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1292772542</t>
+          <t>1244229076</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>0000069759</t>
+          <t>0000011551</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -8123,17 +8123,17 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>94052591890</t>
+          <t>87010769893</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2024-01-30</t>
+          <t>20240130</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2024-06-03</t>
+          <t>03/06/2024</t>
         </is>
       </c>
     </row>
@@ -8160,22 +8160,22 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1292851738</t>
+          <t>1244308261</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>0000069856</t>
+          <t>0000011648</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -8185,22 +8185,22 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>95062693248</t>
+          <t>88021471245</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2021-09-21</t>
+          <t>21/09/2021</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t/>
+          <t>2015/17/05</t>
         </is>
       </c>
     </row>
@@ -8227,22 +8227,22 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Wojciechowska</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1292930923</t>
+          <t>1244387450</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>0000069953</t>
+          <t>0000011745</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8257,17 +8257,17 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>96072794633</t>
+          <t>89032172631</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2018-01-03</t>
+          <t>2018/03/01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t/>
+          <t>24-06-2016</t>
         </is>
       </c>
     </row>
@@ -8299,17 +8299,17 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Cieślicka</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1293010113</t>
+          <t>1244466646</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>0000070050</t>
+          <t>0000011842</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8324,17 +8324,17 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>97082895981</t>
+          <t>90042873980</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2022-02-02</t>
+          <t>02-02-2022</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t/>
+          <t>2017-03-07</t>
         </is>
       </c>
     </row>
@@ -8361,22 +8361,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Jasieńska</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1293089304</t>
+          <t>1244545831</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>0000070147</t>
+          <t>0000011939</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8391,17 +8391,17 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>98090197373</t>
+          <t>91050775374</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2018-09-01</t>
+          <t>2018-01-09</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>20250501</t>
         </is>
       </c>
     </row>
@@ -8428,22 +8428,22 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1293168498</t>
+          <t>1244625027</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>0000070244</t>
+          <t>0000012036</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8458,17 +8458,17 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>99100298723</t>
+          <t>92061476722</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>20181013</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>26/10/2025</t>
         </is>
       </c>
     </row>
@@ -8495,22 +8495,22 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1293247683</t>
+          <t>1244704212</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>0000070341</t>
+          <t>0000012133</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8525,17 +8525,17 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>00310300117</t>
+          <t>93072178119</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2021-01-23</t>
+          <t>23/01/2021</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>2024-01-15</t>
+          <t>2024/15/01</t>
         </is>
       </c>
     </row>
@@ -8562,22 +8562,22 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1293326879</t>
+          <t>1244783401</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>0000070438</t>
+          <t>0000012230</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8592,17 +8592,17 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>01320401465</t>
+          <t>94082879469</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2023-01-01</t>
+          <t>2023/01/01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t/>
+          <t>03-11-2021</t>
         </is>
       </c>
     </row>
@@ -8629,22 +8629,22 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Kozłowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1293406064</t>
+          <t>1244862595</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>0000070535</t>
+          <t>0000012327</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>02210502855</t>
+          <t>95090780855</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2022-02-20</t>
+          <t>20-02-2022</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t/>
+          <t>2022-10-12</t>
         </is>
       </c>
     </row>
@@ -8696,22 +8696,22 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1293485253</t>
+          <t>1244941780</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>0000070632</t>
+          <t>0000012424</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8726,17 +8726,17 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>03220604203</t>
+          <t>96101482207</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2023-11-26</t>
+          <t>2023-26-11</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
+          <t>20250313</t>
         </is>
       </c>
     </row>
@@ -8763,22 +8763,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1293564449</t>
+          <t>1245020970</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>0000070729</t>
+          <t>0000012521</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>04230705599</t>
+          <t>97112183594</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2025-05-02</t>
+          <t>20250502</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t/>
+          <t>24/02/2024</t>
         </is>
       </c>
     </row>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1293643634</t>
+          <t>1245100166</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>0000070826</t>
+          <t>0000012618</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8860,17 +8860,17 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>05240806946</t>
+          <t>98122884943</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2018-09-06</t>
+          <t>06/09/2018</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t/>
+          <t>2025/03/03</t>
         </is>
       </c>
     </row>
@@ -8897,22 +8897,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1293802015</t>
+          <t>1245179357</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>0000070923</t>
+          <t>0000012715</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8927,17 +8927,17 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>60050908338</t>
+          <t>99010786332</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2023/14/10</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2025-02-15</t>
+          <t>15-02-2025</t>
         </is>
       </c>
     </row>
@@ -8964,22 +8964,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1293802015</t>
+          <t>1245258542</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>0000071020</t>
+          <t>0000012812</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8994,17 +8994,17 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>61061009685</t>
+          <t>00221487686</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
+          <t>07-04-2022</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t/>
+          <t>2015-17-05</t>
         </is>
       </c>
     </row>
@@ -9031,22 +9031,22 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1293881204</t>
+          <t>1245337738</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>0000071117</t>
+          <t>0000012909</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -9061,17 +9061,17 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>62071111074</t>
+          <t>01232189073</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2019-06-28</t>
+          <t>2019-28-06</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>20241016</t>
         </is>
       </c>
     </row>
@@ -9098,22 +9098,22 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Duda</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>1293960398</t>
+          <t>1245416923</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>0000071214</t>
+          <t>0000013006</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9128,17 +9128,17 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>63081212421</t>
+          <t>02242890425</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>20200917</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>28/03/2026</t>
         </is>
       </c>
     </row>
@@ -9165,22 +9165,22 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1294118775</t>
+          <t>1245496112</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>0000071311</t>
+          <t>0000013103</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -9195,17 +9195,17 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>64091313816</t>
+          <t>03250791818</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2020-07-14</t>
+          <t>14/07/2020</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-11-07</t>
+          <t>2026/07/11</t>
         </is>
       </c>
     </row>
@@ -9232,29 +9232,29 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Stępień</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>1245575308</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>0000013200</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
           <t>Monika</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Jankowska</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>1294118775</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>0000071408</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Monika</t>
-        </is>
-      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>Michalska</t>
@@ -9262,17 +9262,17 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>65101415168</t>
+          <t>04261493168</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2022-04-18</t>
+          <t>2022/18/04</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t/>
+          <t>17-09-2019</t>
         </is>
       </c>
     </row>
@@ -9299,22 +9299,22 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Kaolina</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1294197964</t>
+          <t>1245654491</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0000071505</t>
+          <t>0000013297</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9329,17 +9329,17 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>66111516553</t>
+          <t>05272194554</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2018-11-25</t>
+          <t>25-11-2018</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
+          <t>2025-15-03</t>
         </is>
       </c>
     </row>
@@ -9366,22 +9366,22 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Szymański</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>1294356345</t>
+          <t>1245733687</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>0000071602</t>
+          <t>0000013394</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9396,17 +9396,17 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>67121617900</t>
+          <t>60082895909</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2022-12-11</t>
+          <t>2022-11-12</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t/>
+          <t>20211103</t>
         </is>
       </c>
     </row>
@@ -9433,22 +9433,22 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Michał</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1294356345</t>
+          <t>1245812872</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>0000071699</t>
+          <t>0000013491</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9463,17 +9463,17 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>68011719292</t>
+          <t>61090797294</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2019-07-26</t>
+          <t>20190726</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>02/10/2026</t>
         </is>
       </c>
     </row>
@@ -9500,22 +9500,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Grzegorz</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Wiśniewski</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>1294435530</t>
+          <t>1245892061</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>0000071796</t>
+          <t>0000013588</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9530,17 +9530,17 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>69021820642</t>
+          <t>62101498645</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2019-09-19</t>
+          <t>19/09/2019</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t/>
+          <t>2023/17/01</t>
         </is>
       </c>
     </row>
@@ -9567,22 +9567,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>1294514726</t>
+          <t>1245971257</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>0000071893</t>
+          <t>0000013685</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9597,17 +9597,17 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>70031922037</t>
+          <t>63112100035</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2018-02-18</t>
+          <t>2018/18/02</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>13-09-2026</t>
         </is>
       </c>
     </row>
@@ -9634,22 +9634,22 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Sebastian</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1294593915</t>
+          <t>1246050447</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>0000071990</t>
+          <t>0000013782</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9664,17 +9664,17 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>71042023384</t>
+          <t>64122801385</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2019-12-13</t>
+          <t>13-12-2019</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-03-03</t>
         </is>
       </c>
     </row>
@@ -9701,22 +9701,22 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>arta</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>1294673100</t>
+          <t>1246129634</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>0000072087</t>
+          <t>0000013879</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9731,17 +9731,17 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>72052124779</t>
+          <t>65010702773</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2019-03-08</t>
+          <t>2019-08-03</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t/>
+          <t>20260410</t>
         </is>
       </c>
     </row>
@@ -9768,29 +9768,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Pietrzak</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>1246288019</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>0000013976</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
           <t>Ewa</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Zielińska</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>1294752294</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>0000072184</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Ewa</t>
-        </is>
-      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>Rutkowska</t>
@@ -9798,17 +9798,17 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>73062226127</t>
+          <t>66021404122</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2021-12-16</t>
+          <t>20211216</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>2025-06-02</t>
+          <t>02/06/2025</t>
         </is>
       </c>
     </row>
@@ -9840,17 +9840,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Grabowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>1294910675</t>
+          <t>1246288019</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>0000072281</t>
+          <t>0000014073</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9865,17 +9865,17 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>74072327512</t>
+          <t>67032105518</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2019-05-10</t>
+          <t>10/05/2019</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025/10/12</t>
         </is>
       </c>
     </row>
@@ -9902,22 +9902,22 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1294910675</t>
+          <t>1246367204</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>0000072378</t>
+          <t>0000014170</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9932,17 +9932,17 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>75082428860</t>
+          <t>68042806868</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
+          <t>2020/22/10</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t/>
+          <t>03-07-2017</t>
         </is>
       </c>
     </row>
@@ -9969,22 +9969,22 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1294989866</t>
+          <t>1246446398</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>0000072475</t>
+          <t>000001426</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9999,17 +9999,17 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>76092530259</t>
+          <t>69050708252</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2022-12-14</t>
+          <t>14-12-2022</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t/>
+          <t>2018-10-08</t>
         </is>
       </c>
     </row>
@@ -10036,22 +10036,22 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Magdalena</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1295069056</t>
+          <t>1246525583</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>0000072572</t>
+          <t>0000014364</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>77102631609</t>
+          <t>70061409609</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2024-08-09</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>20260220</t>
         </is>
       </c>
     </row>
@@ -10103,22 +10103,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Wojciechowska</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>1295148241</t>
+          <t>1246604779</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>0000072669</t>
+          <t>0000014461</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10133,24 +10133,24 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>78112732995</t>
+          <t>71072110999</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2018-01-30</t>
+          <t>20180130</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t/>
+          <t>24/10/2020</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>48021055/P/595006</t>
+          <t/>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10170,22 +10170,22 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Justyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t/>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>1295227437</t>
+          <t>1246683968</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>0000072766</t>
+          <t>0000014558</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -10200,17 +10200,17 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>79122834343</t>
+          <t>72082812349</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2023-07-03</t>
+          <t>03/07/2023</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t/>
+          <t>2021/03/11</t>
         </is>
       </c>
     </row>
@@ -10237,22 +10237,22 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>1295306622</t>
+          <t>1246763153</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>0000072863</t>
+          <t>0000014655</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -10267,17 +10267,17 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>80010135738</t>
+          <t>73090713732</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2020-01-22</t>
+          <t>2020/22/01</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t/>
+          <t>10-12-2022</t>
         </is>
       </c>
     </row>
@@ -10304,22 +10304,22 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>1295385811</t>
+          <t>1246842349</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>0000072960</t>
+          <t>0000014752</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -10334,17 +10334,17 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>81020237087</t>
+          <t>74101415085</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2018-08-22</t>
+          <t>22-08-2018</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2025-21-01</t>
         </is>
       </c>
     </row>
@@ -10371,22 +10371,22 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>1295465007</t>
+          <t>1246921534</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>0000073057</t>
+          <t>0000014849</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10401,17 +10401,17 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>82030338472</t>
+          <t>75112116471</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2021-08-30</t>
+          <t>2021-30-08</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t/>
+          <t>20240224</t>
         </is>
       </c>
     </row>
@@ -10438,22 +10438,22 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Kowalska</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>1295544190</t>
+          <t>1247000724</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>0000073154</t>
+          <t>0000014946</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10468,17 +10468,17 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>83040439829</t>
+          <t>76122817820</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2019-05-18</t>
+          <t>20190518</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>24/02/2026</t>
         </is>
       </c>
     </row>
@@ -10505,22 +10505,22 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1295623386</t>
+          <t>1247079915</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>0000073251</t>
+          <t>0000015043</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10535,17 +10535,17 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>84050541218</t>
+          <t>77010719219</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2019-09-16</t>
+          <t>16/09/2019</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026/10/11</t>
         </is>
       </c>
     </row>
@@ -10572,22 +10572,22 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>1295702571</t>
+          <t>1247159100</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>0000073348</t>
+          <t>0000015140</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10602,17 +10602,17 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>85060642566</t>
+          <t>78021420561</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2020-03-15</t>
+          <t>2020/15/03</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>2025-09-05</t>
+          <t>05-09-2025</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10629,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PZU AS</t>
+          <t>PZU SA</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10639,22 +10639,22 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Łuaksz</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mauzr</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1295781760</t>
+          <t>1247238294</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>0000073445</t>
+          <t>0000015237</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10669,17 +10669,17 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>86070743951</t>
+          <t>79032121957</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2019-01-04</t>
+          <t>04-01-2019</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t/>
+          <t>2016-24-06</t>
         </is>
       </c>
     </row>
@@ -10706,22 +10706,22 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1295860956</t>
+          <t>2247396679</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>0000073542</t>
+          <t>0000015334</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10736,17 +10736,17 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>87080845309</t>
+          <t>80042823306</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2019-05-11</t>
+          <t>2019-11-05</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>20250204</t>
         </is>
       </c>
     </row>
@@ -10773,22 +10773,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Natalia</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kwiatkowska</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1295940141</t>
+          <t>1247396679</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>0000073639</t>
+          <t>0000015431</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10803,17 +10803,17 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>98090946695</t>
+          <t>91050724690</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2018-03-10</t>
+          <t>20180310</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t/>
+          <t>10/08/2018</t>
         </is>
       </c>
     </row>
@@ -10840,22 +10840,22 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1296019333</t>
+          <t>1247475864</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>0000073736</t>
+          <t>0000015528</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10865,22 +10865,22 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>89101048045</t>
+          <t>82061426049</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2022-03-02</t>
+          <t>02/03/2022</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t/>
+          <t>17-09-2019 08:56:36</t>
         </is>
       </c>
     </row>
@@ -10907,22 +10907,22 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Paulina</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Cieślar</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1296098522</t>
+          <t>1247634245</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>0000073833</t>
+          <t>0000015625</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10937,17 +10937,17 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>90111149439</t>
+          <t>83072127435</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2021-07-04</t>
+          <t>2021/04/07</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t/>
+          <t>24-10-2020</t>
         </is>
       </c>
     </row>
@@ -10974,29 +10974,29 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Szymańska</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>1247634245</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>0000015722</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Kozłowska</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>1296177718</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>0000073930</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Katarzyna</t>
-        </is>
-      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>Wiśniewska</t>
@@ -11004,17 +11004,17 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>91121250780</t>
+          <t>84082828785</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2018-11-01</t>
+          <t>01-11-2018</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-27-02</t>
         </is>
       </c>
     </row>
@@ -11041,22 +11041,22 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>1296256903</t>
+          <t>1247713430</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>0000074027</t>
+          <t>0000015819</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -11071,17 +11071,17 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>92011352171</t>
+          <t>85090730172</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2020-02-25</t>
+          <t>2020-25-02</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t/>
+          <t>20221210</t>
         </is>
       </c>
     </row>
@@ -11108,22 +11108,22 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>1296336097</t>
+          <t>1247871815</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>0000074124</t>
+          <t>0000015916</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -11138,17 +11138,17 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>93021453528</t>
+          <t>86101431523</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>20220831</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t/>
+          <t>17/01/2023</t>
         </is>
       </c>
     </row>
@@ -11175,22 +11175,22 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Małgorzata</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>2296415282</t>
+          <t>1247871815</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>0000074221</t>
+          <t>0000016013</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -11205,17 +11205,17 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>94031554913</t>
+          <t>87112132919</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2021-08-18</t>
+          <t>18/08/2021</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t/>
+          <t>2024/24/02</t>
         </is>
       </c>
     </row>
@@ -11242,22 +11242,22 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Iwona</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Nowacka</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>1296494471</t>
+          <t>1247951000</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>0000074318</t>
+          <t>0000016110</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -11272,17 +11272,17 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>95041656262</t>
+          <t>88122834260</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-13-07 08:32</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t/>
+          <t>03-03-2025</t>
         </is>
       </c>
     </row>
@@ -11309,22 +11309,22 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1296573667</t>
+          <t>1248030199</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>0000074415</t>
+          <t>0000016207</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -11339,17 +11339,17 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>96051757657</t>
+          <t>89010735658</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2021-08-09</t>
+          <t>09-08-2021</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -11376,22 +11376,22 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1296652852</t>
+          <t>1248109386</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>0000074512</t>
+          <t>0000016304</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -11406,17 +11406,17 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>97061859005</t>
+          <t>90021437006</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
+          <t>2022-07-04</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>20251120</t>
         </is>
       </c>
     </row>
@@ -11443,22 +11443,22 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>1296732048</t>
+          <t>1248188575</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>0000074609</t>
+          <t>0000016401</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11473,17 +11473,17 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>98071960394</t>
+          <t>91032138393</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2020-05-25</t>
+          <t>20200525</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>11/08/2026</t>
         </is>
       </c>
     </row>
@@ -11510,22 +11510,22 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Maria</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>1296811233</t>
+          <t>1248267760</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>0000074706</t>
+          <t>0000016498</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11540,17 +11540,17 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>99082061740</t>
+          <t>92042839742</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2020-10-24</t>
+          <t>24/10/2020</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t/>
+          <t>2017/03/07</t>
         </is>
       </c>
     </row>
@@ -11577,22 +11577,22 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>1296890422</t>
+          <t>1248346956</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>0000074803</t>
+          <t>0000016595</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11607,17 +11607,17 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>00292163131</t>
+          <t>93050741139</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2019-09-09</t>
+          <t>2019/09/09</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>17-10-2024</t>
         </is>
       </c>
     </row>
@@ -11644,22 +11644,22 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Kozłowski</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>1297127993</t>
+          <t>1248426141</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>0000074900</t>
+          <t>0000016692</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>01302264482</t>
+          <t>94061442488</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2022-02-24</t>
+          <t>24-02-2022</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -11711,22 +11711,22 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dąbrowska</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>1297127993</t>
+          <t>1248505337</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>0000074997</t>
+          <t>0000016789</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11741,17 +11741,17 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>02312365877</t>
+          <t>95072143874</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2022-06-15</t>
+          <t>2022-15-06</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>20240808</t>
         </is>
       </c>
     </row>
@@ -11778,22 +11778,22 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Elżbieta</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>1297127993</t>
+          <t>1248584526</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>0000075094</t>
+          <t>0000016886</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11808,17 +11808,17 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>03322467225</t>
+          <t>96082845224</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2020-03-15</t>
+          <t>20200315</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>24/05/2026</t>
         </is>
       </c>
     </row>
@@ -11845,22 +11845,22 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Zielińska</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>1297207189</t>
+          <t>1248663711</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>0000075191</t>
+          <t>0000016983</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11875,17 +11875,17 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>04212568615</t>
+          <t>97090746617</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>04/12/2024</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t/>
+          <t>2022/10/12</t>
         </is>
       </c>
     </row>
@@ -11912,22 +11912,22 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Łukasz</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>1297286378</t>
+          <t>1248742907</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>0000075288</t>
+          <t>0000017080</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11942,17 +11942,17 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>05222669963</t>
+          <t>98101447969</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2022-03-24</t>
+          <t>2022/24/03</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>03-09-2025</t>
         </is>
       </c>
     </row>
@@ -11979,22 +11979,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Wojciech</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>1297365563</t>
+          <t>1248822090</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>0000075385</t>
+          <t>0000017177</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -12009,17 +12009,17 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>60032771358</t>
+          <t>99112149356</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2021-09-22</t>
+          <t>22-09-2021</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-24-04</t>
         </is>
       </c>
     </row>
@@ -12051,17 +12051,17 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>1297444759</t>
+          <t>1248901286</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>0000075482</t>
+          <t>0000017274</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -12076,17 +12076,17 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>61042872705</t>
+          <t>00322850703</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2019-05-29</t>
+          <t>2019-29-05</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>20250901</t>
         </is>
       </c>
     </row>
@@ -12113,22 +12113,22 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Jan</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1297523944</t>
+          <t>1248980475</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>0000075579</t>
+          <t>0000017371</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -12143,17 +12143,17 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>62050174098</t>
+          <t>01210752093</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2019-05-08</t>
+          <t>20190508</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t/>
+          <t>10/04/2026</t>
         </is>
       </c>
     </row>
@@ -12180,22 +12180,22 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1297682329</t>
+          <t>1249059667</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>0000075676</t>
+          <t>0000017468</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -12210,17 +12210,17 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>63060275445</t>
+          <t>02221453441</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2021-08-14</t>
+          <t>14/08/2021</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2025-01-13</t>
+          <t>2025/13/01</t>
         </is>
       </c>
     </row>
@@ -12247,22 +12247,22 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Marta</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Pawłowska</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>1297682329</t>
+          <t>1249138852</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>0000075773</t>
+          <t>0000017565</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -12277,17 +12277,17 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>64070376830</t>
+          <t>03232154837</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2021-10-29</t>
+          <t>2021/29/10</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>18-03-2026</t>
         </is>
       </c>
     </row>
@@ -12314,22 +12314,22 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>1297761514</t>
+          <t>1249218048</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>0000075870</t>
+          <t>0000017662</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -12344,17 +12344,17 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>65080478189</t>
+          <t>04242856188</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>17-09-2022</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2024-04-05</t>
         </is>
       </c>
     </row>
@@ -12381,22 +12381,22 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>1297919895</t>
+          <t>1249297237</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>0000075967</t>
+          <t>0000017759</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -12411,17 +12411,17 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>66090579574</t>
+          <t>05250757571</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2021-12-25</t>
+          <t>2021-25-12</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>20251017</t>
         </is>
       </c>
     </row>
@@ -12448,22 +12448,22 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aleksandra</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>1297919895</t>
+          <t>1249376422</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>0000076064</t>
+          <t>0000017856</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12478,17 +12478,17 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>67100680927</t>
+          <t>60061458925</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2021-06-06</t>
+          <t>20210606</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t/>
+          <t>17/09/2019</t>
         </is>
       </c>
     </row>
@@ -12515,22 +12515,22 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Cieślicki</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>1297999084</t>
+          <t>1249455618</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>0000076161</t>
+          <t>0000017953</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -12545,17 +12545,17 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>68110782313</t>
+          <t>61072160315</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2019-01-06</t>
+          <t>06/01/2019</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>2026-11-21</t>
+          <t>2026/21/11</t>
         </is>
       </c>
     </row>
@@ -12582,22 +12582,22 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>1298078274</t>
+          <t>1249534803</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>0000076258</t>
+          <t>0000018050</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -12612,17 +12612,17 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>69120883661</t>
+          <t>62082861665</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2022-09-28</t>
+          <t>2022/28/09</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>29-03-2026</t>
         </is>
       </c>
     </row>
@@ -12649,22 +12649,22 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Jasieński</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>1298236655</t>
+          <t>1249613997</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>0000076355</t>
+          <t>0000018147</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12679,17 +12679,17 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>70010985051</t>
+          <t>63090763059</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
+          <t>26-01-2022</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-18-02</t>
         </is>
       </c>
     </row>
@@ -12721,17 +12721,17 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>1298236655</t>
+          <t>1249693186</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>0000076452</t>
+          <t>0000018244</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12746,17 +12746,17 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>71021086407</t>
+          <t>64101464400</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-01-04</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t/>
+          <t>20230117</t>
         </is>
       </c>
     </row>
@@ -12783,22 +12783,22 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Pawlik</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>1298315840</t>
+          <t>1249772371</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>0000076549</t>
+          <t>0000018341</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12813,17 +12813,17 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>72031187793</t>
+          <t>65112165797</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>2018-03-10</t>
+          <t>20180310</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t/>
+          <t>24/02/2024</t>
         </is>
       </c>
     </row>
@@ -12850,22 +12850,22 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Nowak</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>1298474225</t>
+          <t>1249851567</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>0000076646</t>
+          <t>0000018438</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12880,17 +12880,17 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>73041289141</t>
+          <t>66122867147</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2020-12-04</t>
+          <t>04/12/2020</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t/>
+          <t>2025/03/03</t>
         </is>
       </c>
     </row>
@@ -12922,17 +12922,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>1298474225</t>
+          <t>1249930752</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>0000076743</t>
+          <t>0000018535</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12947,17 +12947,17 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>74051390539</t>
+          <t>67010768535</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>2023-04-21</t>
+          <t>2023/21/04</t>
         </is>
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t/>
+          <t>10-04-2026</t>
         </is>
       </c>
     </row>
@@ -12984,22 +12984,22 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Agnieszka</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Jankowska</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>1298553410</t>
+          <t>1250009942</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>0000076840</t>
+          <t>0000018632</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -13014,17 +13014,17 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>75061491887</t>
+          <t>68021469884</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2020-10-26</t>
+          <t>26-10-2020</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t/>
+          <t>2015-17-05</t>
         </is>
       </c>
     </row>
@@ -13051,22 +13051,22 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>1298632606</t>
+          <t>1250089131</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>0000076937</t>
+          <t>0000018729</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -13081,17 +13081,17 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>76071593273</t>
+          <t>69032171274</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2021-07-28</t>
+          <t>2021-28-07</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>20251203</t>
         </is>
       </c>
     </row>
@@ -13118,22 +13118,22 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Dariusz</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Piotrowski</t>
+          <t>Kowalska</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>1298790989</t>
+          <t>1250168327</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>0000077034</t>
+          <t>0000018826</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>77081694620</t>
+          <t>70042872622</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2018-01-23</t>
+          <t>20180123</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t/>
+          <t>03/07/2017</t>
         </is>
       </c>
     </row>
@@ -13185,22 +13185,22 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>1298790989</t>
+          <t>1250247512</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>0000077131</t>
+          <t>0000018923</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -13215,17 +13215,17 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>78091796016</t>
+          <t>71050774016</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t/>
+          <t>2018/10/08</t>
         </is>
       </c>
     </row>
@@ -13252,22 +13252,22 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Mateusz</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Kozłowski</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>1298870174</t>
+          <t>1250326708</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>0000077228</t>
+          <t>0000019020</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -13282,17 +13282,17 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>79101897367</t>
+          <t>72061475365</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2022-08-30</t>
+          <t>2022/30/08</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t/>
+          <t>17-09-2019</t>
         </is>
       </c>
     </row>
@@ -13319,22 +13319,22 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Jakub</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>1298949361</t>
+          <t>1250405891</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>0000077325</t>
+          <t>000001911</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -13349,17 +13349,17 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>80111998751</t>
+          <t>73072176751</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>2021-07-16</t>
+          <t>16-07-2021</t>
         </is>
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-15-10</t>
         </is>
       </c>
     </row>
@@ -13386,22 +13386,22 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Joanna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kamińska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>1299028551</t>
+          <t>1250485080</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>0000077422</t>
+          <t>0000019214</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -13416,17 +13416,17 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>81122000101</t>
+          <t>74082878101</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>2020-03-08</t>
+          <t>2020-08-03</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t/>
+          <t>20211103</t>
         </is>
       </c>
     </row>
@@ -13453,22 +13453,22 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Bartosz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>1299107747</t>
+          <t>1250564276</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>0000077519</t>
+          <t>0000019311</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -13483,17 +13483,17 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>82012101492</t>
+          <t>75090779495</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>20240411</t>
         </is>
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t/>
+          <t>10/12/2022</t>
         </is>
       </c>
     </row>

--- a/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_pracownik_agenta.xlsx
+++ b/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_pracownik_agenta.xlsx
@@ -120,12 +120,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lewandowska-Król</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -187,12 +187,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -254,12 +254,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -321,12 +321,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -388,12 +388,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -455,12 +455,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PZU AS</t>
+          <t>PZU SA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -589,12 +589,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -656,12 +656,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -723,12 +723,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>79112119190</t>
+          <t>69112119190</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -790,17 +790,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2235597366</t>
+          <t>1235597366</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1235676551</t>
+          <t>2235676551</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1192,12 +1192,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1326,12 +1326,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1393,12 +1393,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1728,12 +1728,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1862,12 +1862,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2197,12 +2197,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0000003597</t>
+          <t>000000359</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lewandowska-Król</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>000000456</t>
+          <t>0000004567</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3671,12 +3671,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UNIQ  .A.</t>
+          <t>UNI  .A.</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Marke</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4073,17 +4073,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2239477676</t>
+          <t>1239477676</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>83010787692</t>
+          <t>73010787692</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -4207,17 +4207,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1239636057</t>
+          <t>2239636057</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4743,12 +4743,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4944,12 +4944,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lewandowska-Król</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5609,22 +5609,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Aleksandra Pawłowska Konsulting</t>
+          <t/>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t/>
+          <t>1241299047</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -5748,12 +5748,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5882,17 +5882,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t/>
+          <t>1241615809</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0000008447</t>
+          <t>000000844</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6016,17 +6016,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1241774181</t>
+          <t/>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -6485,12 +6485,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>000000941</t>
+          <t>0000009417</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>67050742490</t>
+          <t>77050742490</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7088,12 +7088,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -7314,7 +7314,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Ostorwski</t>
+          <t>Ostroswki</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -7356,12 +7356,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -7423,17 +7423,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>2243516365</t>
+          <t>1243516365</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>87032156193</t>
+          <t>77032156193</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -7557,17 +7557,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1243595554</t>
+          <t>2243595554</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -8026,12 +8026,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -8093,12 +8093,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lewandowska-Król</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -8227,12 +8227,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -8361,12 +8361,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -8830,12 +8830,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -8964,12 +8964,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -9098,12 +9098,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>0000013297</t>
+          <t>000001329</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -9433,12 +9433,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -9500,12 +9500,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -9567,12 +9567,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -9768,12 +9768,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -9969,12 +9969,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>000001426</t>
+          <t>0000014267</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -10036,12 +10036,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -10170,12 +10170,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -10572,12 +10572,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>PZU SA</t>
+          <t>PZU AS</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -10639,12 +10639,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -10664,7 +10664,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Saodwski</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -10706,17 +10706,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>2247396679</t>
+          <t>1247396679</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10773,12 +10773,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -10803,7 +10803,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>91050724690</t>
+          <t>81050724690</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -10840,12 +10840,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Lewandowska-Król</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1247634245</t>
+          <t>2247634245</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -11108,12 +11108,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -11376,12 +11376,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -11443,12 +11443,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -11510,12 +11510,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11577,12 +11577,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -11644,12 +11644,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -11711,12 +11711,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -11845,12 +11845,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -11979,12 +11979,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -12113,12 +12113,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -12180,12 +12180,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -12247,12 +12247,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -12314,12 +12314,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -12448,12 +12448,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Pietrzak</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -12515,12 +12515,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Wójcicki</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Czarnecka</t>
+          <t>Piątek</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lis</t>
+          <t>Sadowski</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -12664,7 +12664,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>0000018147</t>
+          <t>000001814</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12716,12 +12716,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Kołodziej</t>
+          <t>Włodarczyk</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -12783,12 +12783,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Kaczmarek</t>
+          <t>Borkowski</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -12850,12 +12850,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Monika</t>
+          <t>Anna</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Piątek</t>
+          <t>Kowalska-Krawczyk</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -12917,12 +12917,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Marek</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Sadowski</t>
+          <t>Nowacki</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Barbara</t>
+          <t>Katarzyna</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Włodarczyk</t>
+          <t>Wiśniewska</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Rafał</t>
+          <t>Krzysztof</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Borkowski</t>
+          <t>Wójcik</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Anna</t>
+          <t>Ewa</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Kowalska</t>
+          <t>Kowalczyk</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -13185,12 +13185,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Kamiński</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Monika</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Lewandowska</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Krzysztof</t>
+          <t>Marek</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>000001911</t>
+          <t>0000019117</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Ewa</t>
+          <t>Barbara</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -13453,12 +13453,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Rafał</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">

--- a/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_pracownik_agenta.xlsx
+++ b/data/xlsx/KNF_Rejestr_posrednikow_ubezpieczeniowych_pracownik_agenta.xlsx
@@ -130,7 +130,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -155,12 +155,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Kowalska-Krawczyk</t>
+          <t>Lewandowska-Król</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>60021406849</t>
+          <t>62021428841</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -187,7 +187,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zielony Bieszczady S.A.</t>
+          <t>Pewny Delfin S.A.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -202,7 +202,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -227,12 +227,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Nowacki</t>
+          <t>Zieliński</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>61032108236</t>
+          <t>63032130231</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -259,7 +259,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Zielony Karpaty SA</t>
+          <t>Dobry Koral SA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -274,7 +274,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -299,12 +299,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Wiśniewska</t>
+          <t>Szymańska</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>62042809586</t>
+          <t>64042831581</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -331,7 +331,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Zielony Bałtyk S. A.</t>
+          <t>Polski Szafir S. A.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -346,7 +346,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -371,12 +371,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Wójcik</t>
+          <t>Dąbrowski</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>63050710972</t>
+          <t>65050732974</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -403,7 +403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zielony Sudety Spółka Akcyjna</t>
+          <t>Europejski Orzeł Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -418,7 +418,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -443,12 +443,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Kowalczyk</t>
+          <t>Mazur</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>64061412321</t>
+          <t>66061434323</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -475,7 +475,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Niebieski Amber sp. z o.o.</t>
+          <t>Globalny Kaktus sp. z o.o.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -515,12 +515,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Kamiński</t>
+          <t>Krawczyk</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>65072113717</t>
+          <t>67072135719</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Niebieski Bizon sp z oo</t>
+          <t>Lokalny Olimp sp z oo</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -587,12 +587,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Lewandowska</t>
+          <t>Woźniak</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>66082815068</t>
+          <t>68082837060</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Niebieski Canyon sp. z o. o.</t>
+          <t>Nowoczesny Beskid sp. z o. o.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jankoswki</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -659,12 +659,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Zieliński</t>
+          <t>Jankowski</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>67090716451</t>
+          <t>69090738453</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Niebieski Delfin Sp. z o.o.</t>
+          <t>Tradycyjny Canyon Sp. z o.o.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Szymańska</t>
+          <t>Grabowska</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>68101417802</t>
+          <t>70101439803</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Niebieski Echo SP Z O O</t>
+          <t>Dynamiczny Jantar SP Z O O</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Dąbrowski</t>
+          <t>Pawlak</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>69112119190</t>
+          <t>71112141194</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Niebieski Falcon spółka z ograniczoną odpowiedzialnością</t>
+          <t>Stabilny Rubin spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -875,12 +875,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Mazur</t>
+          <t>Michalska</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>70122820541</t>
+          <t>72122842543</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Niebieski Gryf Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Innowacyjny Sokół Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Krawczyk</t>
+          <t>Król</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>71010721939</t>
+          <t>73010743931</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Niebieski Horyzont S.A.</t>
+          <t>Kreatywny Jodełka S.A.</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Woźniak</t>
+          <t>Wieczorek</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>72021423289</t>
+          <t>74021445281</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Niebieski Ikar SA</t>
+          <t>Aktywny Zodiak SA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Jankowski</t>
+          <t>Jabłoński</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>73032124675</t>
+          <t>75032146677</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Niebieski Jantar S. A.</t>
+          <t>Jasny Kasprowy S. A.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Grabowska</t>
+          <t>Witkowska</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>74042826025</t>
+          <t>76042848027</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Niebieski Koral Spółka Akcyjna</t>
+          <t>Green Bizon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pawlak</t>
+          <t>Walczak</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>75050727418</t>
+          <t>77050749410</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Niebieski Lotos sp. z o.o.</t>
+          <t>Blue Ikar sp. z o.o.</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1307,12 +1307,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Michalska</t>
+          <t>Stępień</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>76061428767</t>
+          <t>78061450762</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Niebieski Magnolia sp z oo</t>
+          <t>Gold Pegaz sp z oo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1379,12 +1379,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Król</t>
+          <t>Baran</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>77072130157</t>
+          <t>79072152159</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Niebieski Neon sp. z o. o.</t>
+          <t>Silver Żubr sp. z o. o.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Wieczorek</t>
+          <t>Rutkowska</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>78082831506</t>
+          <t>80082853507</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Niebieski Oaza Sp. z o.o.</t>
+          <t>Smart Narew Sp. z o.o.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Jabłoński</t>
+          <t>Górski</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>79090732890</t>
+          <t>81090754891</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P.P.H.U. Niebieski Pegaz</t>
+          <t>P.P.H.U. Fast Syrena</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Witkowska</t>
+          <t>Sikora</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>80101434241</t>
+          <t>82101456243</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Niebieski Rubin spółka z ograniczoną odpowiedzialnością</t>
+          <t>Safe Rysy spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Walczak</t>
+          <t>Ostrowski</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>81112135637</t>
+          <t>83112157639</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Niebieski Szafir Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Best Amber Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,12 +1739,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Stępień</t>
+          <t>Tomaszewska</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>82122836987</t>
+          <t>84122858989</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Niebieski Tytan S.A.</t>
+          <t>Global Horyzont S.A.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Baran</t>
+          <t>Zając</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>83010738376</t>
+          <t>85010760371</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Niebieski Uran SA</t>
+          <t>Future Oaza SA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Rutkowska</t>
+          <t>Pietrzak</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>84021439724</t>
+          <t>86021461729</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Niebieski Wektor S. A.</t>
+          <t>Wielkopolski Zefir S. A.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Górski</t>
+          <t>Wójcicki</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>85032141114</t>
+          <t>87032163116</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Niebieski Zefir Spółka Akcyjna</t>
+          <t>Śląski Pilica Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sikora</t>
+          <t>Czarnecka</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>86042842464</t>
+          <t>88042864466</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Niebieski Żubr sp. z o.o.</t>
+          <t>Mazowiecki Marmur sp. z o.o.</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Ostrowski</t>
+          <t>Lis</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>87050743857</t>
+          <t>89050765859</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Niebieski Sokół sp z oo</t>
+          <t>Pomorski Giewont sp z oo</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Tomaszewska</t>
+          <t>Kołodziej</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>88061445206</t>
+          <t>90061467207</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2203,7 +2203,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Niebieski Orzeł sp. z o. o.</t>
+          <t>Dolnośląski Sudety sp. z o. o.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2218,7 +2218,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Zając</t>
+          <t>Kaczmarek</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>89072146593</t>
+          <t>91072168594</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Niebieski Kormoran Sp. z o.o.</t>
+          <t>Karpacki Gryf Sp. z o.o.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2347,7 +2347,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Niebieski Barycz SP Z O O</t>
+          <t>Bałtycki Neon SP Z O O</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Niebieski Noteć spółka z ograniczoną odpowiedzialnością</t>
+          <t>Młody Wektor spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Niebieski Pilica Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wspólny Noteć Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Niebieski Narew S.A.</t>
+          <t>Pierwszy Granit S.A.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Niebieski Jodełka SA</t>
+          <t>Zielony Żubr SA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Niebieski Kaktus S. A.</t>
+          <t>Niebieski Narew S. A.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Niebieski Szmaragd Spółka Akcyjna</t>
+          <t>Złoty Syrena Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Niebieski Topaz sp. z o.o.</t>
+          <t>Srebrny Rysy sp. z o.o.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Niebieski Granit sp z oo</t>
+          <t>Czysty Amber sp z oo</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Niebieski Syrena Sp. z o.o.</t>
+          <t>Pewny Oaza Sp. z o.o.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Niebieski Zodiak SP Z O O</t>
+          <t>Dobry Zefir SP Z O O</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Niebieski Olimp spółka z ograniczoną odpowiedzialnością</t>
+          <t>Polski Pilica spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Niebieski Zorza Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Europejski Marmur Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Niebieski Krokus S.A.</t>
+          <t>Globalny Giewont S.A.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Niebieski Narcyz SA</t>
+          <t>Lokalny Sudety SA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Niebieski Giewont S. A.</t>
+          <t>Nowoczesny Gryf S. A.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Niebieski Rysy Spółka Akcyjna</t>
+          <t>Tradycyjny Neon Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Niebieski Kasprowy sp. z o.o.</t>
+          <t>Dynamiczny Wektor sp. z o.o.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Amber Transport sp. z o. o.</t>
+          <t>Falcon Transport sp. z o. o.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Amber Spedycja Sp. z o.o.</t>
+          <t>Koral Spedycja Sp. z o.o.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Amber Logistyka SP Z O O</t>
+          <t>Pegaz Logistyka SP Z O O</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Amber Handel spółka z ograniczoną odpowiedzialnością</t>
+          <t>Wektor Handel spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Amber Usługi Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Usługi Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Amber Finanse S.A.</t>
+          <t>Jodełka Finanse S.A.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ambre Doradztwo SA</t>
+          <t>Marmur Doradztwo SA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Edward</t>
+          <t>Ewdard</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Amber Szkolenia S. A.</t>
+          <t>Krokus Szkolenia S. A.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Amber Media Spółka Akcyjna</t>
+          <t>Beskid Media Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Amber Marketing sp z oo</t>
+          <t>Falcon Marketing sp z oo</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Amber Druk sp. z o. o.</t>
+          <t>Koral Druk sp. z o. o.</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Amber Informatyka Sp. z o.o.</t>
+          <t>Pegaz Informatyka Sp. z o.o.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Amber Oprogramowanie SP Z O O</t>
+          <t>Wektor Oprogramowanie SP Z O O</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Amber Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Kormoran Rolnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Amber Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Ogrodnictwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Amber Produkcja S.A.</t>
+          <t>Marmur Produkcja S.A.</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Amber Przemysł SA</t>
+          <t>Krokus Przemysł SA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Amber Ekologia S. A.</t>
+          <t>Beskid Ekologia S. A.</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Amber Instalacje sp. z o.o.</t>
+          <t>Falcon Instalacje sp. z o.o.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Amber Nieruchomości sp z oo</t>
+          <t>Koral Nieruchomości sp z oo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Amber Inwestycje sp. z o. o.</t>
+          <t>Pegaz Inwestycje sp. z o. o.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Amber Medycyna Sp. z o.o.</t>
+          <t>Wektor Medycyna Sp. z o.o.</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Amber Zdrowie SP Z O O</t>
+          <t>Kormoran Zdrowie SP Z O O</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amber Urody spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jodełka Urody spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Amber Turystyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Turystyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Amber Rozrywka S.A.</t>
+          <t>Krokus Rozrywka S.A.</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Amber Gastronomia SA</t>
+          <t>Beskid Gastronomia SA</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Amber Tekstylia Spółka Akcyjna</t>
+          <t>Falcon Tekstylia Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6019,12 +6019,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Amber Motoryzacja sp. z o.o.</t>
+          <t>Koral Motoryzacja sp. z o.o.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Aleksandra Pawłowska Konsulting</t>
+          <t/>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t/>
+          <t>98122841184</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Amber Ubezpieczenia sp z oo</t>
+          <t>Pegaz Ubezpieczenia sp z oo</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Amber Spawalnictwo sp. z o. o.</t>
+          <t>Wektor Spawalnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Amber Ślusarstwo Sp. z o.o.</t>
+          <t>Kormoran Ślusarstwo Sp. z o.o.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6307,7 +6307,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Amber Krawiectwo SP Z O O</t>
+          <t>Jodełka Krawiectwo SP Z O O</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Amber Ochrona spółka z ograniczoną odpowiedzialnością</t>
+          <t>Marmur Ochrona spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Amber Catering Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Krokus Catering Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Amber Księgowość S.A.</t>
+          <t>Beskid Księgowość S.A.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bizon Budownictwo SA</t>
+          <t>Jantar Budownictwo SA</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bizon Transport S. A.</t>
+          <t>Oaza Transport S. A.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bizon Spedycja Spółka Akcyjna</t>
+          <t>Uran Spedycja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bizon Logistyka sp. z o.o.</t>
+          <t>Orzeł Logistyka sp. z o.o.</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bizon Handel sp z oo</t>
+          <t>Narew Handel sp z oo</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6955,7 +6955,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bizon Usługi sp. z o. o.</t>
+          <t>Granit Usługi sp. z o. o.</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bizon Finanse Sp. z o.o.</t>
+          <t>Zorza Finanse Sp. z o.o.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bizon Doradztwo SP Z O O</t>
+          <t>Kasprowy Doradztwo SP Z O O</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bizon Szkolenia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sudety Szkolenia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7243,7 +7243,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bizon Media Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Media Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>P.P.H.U. Bizon Reklama</t>
+          <t>P.P.H.U. Jantar Reklama</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bizon Marketing SA</t>
+          <t>Oaza Marketing SA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bizon Druk S. A.</t>
+          <t>Uran Druk S. A.</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bizon Informatyka Spółka Akcyjna</t>
+          <t>Orzeł Informatyka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -7603,7 +7603,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bizon Oprogramowanie sp. z o.o.</t>
+          <t>Narew Oprogramowanie sp. z o.o.</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -7675,7 +7675,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bizon Rolnictwo sp z oo</t>
+          <t>Granit Rolnictwo sp z oo</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bizon Ogrodnictwo sp. z o. o.</t>
+          <t>Zorza Ogrodnictwo sp. z o. o.</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bizon Produkcja Sp. z o.o.</t>
+          <t>Kasprowy Produkcja Sp.  o.o.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bizon Przemysł SP Z O O</t>
+          <t>Sudety Przemysł SP Z O O</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bizon Ekologia spółka z ograniczoną odpowiedzialnością</t>
+          <t>Echo Ekologia spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -8035,7 +8035,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bizon Energetyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Jantar Energetyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bizon Instalacje S.A.</t>
+          <t>Oaza Instalacje S.A.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bizon Nieruchomości SA</t>
+          <t>Uran Nieruchomości SA</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bizon Inwestycje S. A.</t>
+          <t>Orzeł Inwestycje S. A.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bizon Medycyna Spółka Akcyjna</t>
+          <t>Narew Medycyna Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bizon Zdrowie sp. z o.o.</t>
+          <t>Granit Zdrowie sp. z o.o.</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8467,7 +8467,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bizon Urody sp z oo</t>
+          <t>Zorza Urody sp z oo</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bizon Turystyka sp. z o. o.</t>
+          <t>Kasprowy Turystyka sp. z o. o.</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bizon Rozrywka Sp. z o.o.</t>
+          <t>Sudety Rozrywka Sp. z o.o.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -8683,7 +8683,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bizon Gastronomia SP Z O O</t>
+          <t>Echo Gastronomia SP Z O O</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bizon Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Oaza Tekstylia Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bizon Motoryzacja S.A.</t>
+          <t>Uran Motoryzacja S.A.</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bizon Ubezpieczenia SA</t>
+          <t>Orzeł Ubezpieczenia SA</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bizon Spawalnictwo S. A.</t>
+          <t>Narew Spawalnictwo S. A.</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bizon Ślusarstwo Spółka Akcyjna</t>
+          <t>Granit Ślusarstwo Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bizon Krawiectwo sp. z o.o.</t>
+          <t>Zorza Krawiectwo sp. z o.o.</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bizon Ochrona sp z oo</t>
+          <t>Kasprowy Ochrona sp z oo</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bizon Catering sp. z o. o.</t>
+          <t>Sudety Catering sp. z o. o.</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bizon Księgowość Sp. z o.o.</t>
+          <t>Echo Księgowość Sp. z o.o.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Canyon Budownictwo SP Z O O</t>
+          <t>Tytan Budownictwo SP Z O O</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9547,7 +9547,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Canyon Transport spółka z ograniczoną odpowiedzialnością</t>
+          <t>Sokół Transport spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Canyon Spedycja Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Spedycja Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Canyon Logistyka S.A.</t>
+          <t>Topaz Logistyka S.A.</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Canyon Handel SA</t>
+          <t>Olimp Handel SA</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Canyon Usługi S. A.</t>
+          <t>Rysy Usługi S. A.</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Canyon Finanse Spółka Akcyjna</t>
+          <t>Bałtyk Finanse Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Canyon Doradztwo sp. z o.o.</t>
+          <t>Delfin Doradztwo sp. z o.o.</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Canyon Szkolenia sp z oo</t>
+          <t>Ikar Szkolenia sp z oo</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Canyon Media sp. z o. o.</t>
+          <t>Neon Media sp. z o. o.</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PPHU Canyon Reklama</t>
+          <t>PPHU Tytan Reklama</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Canyon Marketing SP Z O O</t>
+          <t>Sokół Marketing SP Z O O</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Canyon Druk spółka z ograniczoną odpowiedzialnością</t>
+          <t>Pilica Druk spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Canyon Informatyka Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Informatyka Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Canyon Oprogramowanie S.A.</t>
+          <t>Olimp Oprogramowanie S.A.</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Canyon Rolnictwo SA</t>
+          <t>Rysy Rolnictwo SA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -10627,7 +10627,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Canyon Ogrodnictwo S. A.</t>
+          <t>Bałtyk Ogrodnictwo S. A.</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Canyon Produkcja Spółka Akcyjna</t>
+          <t>Delfin Produkcja Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Canyon Przemysł sp. z o.o.</t>
+          <t>Ikar Przemysł sp. z o.o.</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Canyon Ekologia sp z oo</t>
+          <t>Neon Ekologia sp z oo</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Canyon Energetyka sp. z o. o.</t>
+          <t>Tytan Energetyka sp. z o. o.</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Canyon Instalacje Sp. z o.o.</t>
+          <t>Sokół Instalacje Sp. z o.o.</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Canyon Nieruchomości SP Z O O</t>
+          <t>Pilica Nieruchomości SP Z O O</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Canyon Inwestycje spółka z ograniczoną odpowiedzialnością</t>
+          <t>Topaz Inwestycje spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11203,7 +11203,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Canyon Medycyna Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Medycyna Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Canyon Zdrowie S.A.</t>
+          <t>Rysy Zdrowie S.A.</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Canyon Urody SA</t>
+          <t>Bałtyk Urody SA</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Canyon Turystyka S. A.</t>
+          <t>Delfin Turystyka S. A.</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Ceazry</t>
+          <t>Cezary</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Canyon Rozrywka Spółka Akcyjna</t>
+          <t>Ikar Rozrywka Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Canyon Gastronomia sp. z o.o.</t>
+          <t>Neon Gastronomia sp. z o.o.</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Canyon Tekstylia sp. z o. o.</t>
+          <t>Sokół Tekstylia sp. z o. o.</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Canyon Motoryzacja Sp. z o.o.</t>
+          <t>Pilica Motoryzacja Sp. z o.o.</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Canyon Ubezpieczenia SP Z O O</t>
+          <t>Topaz Ubezpieczenia SP Z O O</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Canyon Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
+          <t>Olimp Spawalnictwo spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Canyon Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
+          <t>Rysy Ślusarstwo Spółka z ograniczoną odpowiedzialnością</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Canyon Krawiectwo S.A.</t>
+          <t>Bałtyk Krawiectwo S.A.</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Canyon Ochrona SA</t>
+          <t>Delfin Ochrona SA</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Canyon Catering S. A.</t>
+          <t>Ikar Catering S. A.</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Canyon Księgowość Spółka Akcyjna</t>
+          <t>Neon Księgowość Spółka Akcyjna</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>93032160398</t>
+          <t>03032160398</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>04042861747</t>
+          <t>94042861747</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
